--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.74798771141056</v>
+      </c>
+      <c r="C2">
         <v>29.11100136611146</v>
-      </c>
-      <c r="C2">
-        <v>28.74798771141056</v>
       </c>
       <c r="D2">
         <v>3.435127453788363</v>
       </c>
       <c r="E2">
-        <v>18.44114265283652</v>
+        <v>18.21118194117719</v>
       </c>
       <c r="F2">
         <v>63.34767540598629</v>
       </c>
       <c r="G2">
-        <v>18.21118194117719</v>
+        <v>18.44114265283652</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.31365268583433</v>
+      </c>
+      <c r="C3">
         <v>29.03730121894619</v>
-      </c>
-      <c r="C3">
-        <v>30.31365268583433</v>
       </c>
       <c r="D3">
         <v>3.443846218558089</v>
       </c>
       <c r="E3">
-        <v>18.22223244192018</v>
+        <v>19.02320126928648</v>
       </c>
       <c r="F3">
         <v>62.75456628879333</v>
       </c>
       <c r="G3">
-        <v>19.02320126928648</v>
+        <v>18.22223244192018</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.28279118572928</v>
+      </c>
+      <c r="C4">
         <v>36.90975865687303</v>
-      </c>
-      <c r="C4">
-        <v>31.28279118572928</v>
       </c>
       <c r="D4">
         <v>2.709310589907605</v>
       </c>
       <c r="E4">
-        <v>21.94494268111986</v>
+        <v>18.5993917180067</v>
       </c>
       <c r="F4">
         <v>59.45566560087342</v>
       </c>
       <c r="G4">
-        <v>18.5993917180067</v>
+        <v>21.94494268111986</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>38.66900175131349</v>
+      </c>
+      <c r="C5">
         <v>35.30647985989492</v>
-      </c>
-      <c r="C5">
-        <v>38.66900175131349</v>
       </c>
       <c r="D5">
         <v>2.83234126984127</v>
       </c>
       <c r="E5">
-        <v>20.29394000402657</v>
+        <v>22.22669619488625</v>
       </c>
       <c r="F5">
         <v>57.47936380108717</v>
       </c>
       <c r="G5">
-        <v>22.22669619488625</v>
+        <v>20.29394000402657</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.69936228363195</v>
+      </c>
+      <c r="C6">
         <v>36.65350744002429</v>
-      </c>
-      <c r="C6">
-        <v>29.69936228363195</v>
       </c>
       <c r="D6">
         <v>2.728251864125932</v>
       </c>
       <c r="E6">
-        <v>22.03358890105878</v>
+        <v>17.85323110624315</v>
       </c>
       <c r="F6">
         <v>60.11317999269806</v>
       </c>
       <c r="G6">
-        <v>17.85323110624315</v>
+        <v>22.03358890105878</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.20771873105678</v>
+      </c>
+      <c r="C7">
         <v>33.24914124065468</v>
-      </c>
-      <c r="C7">
-        <v>28.20771873105678</v>
       </c>
       <c r="D7">
         <v>3.007596475235491</v>
       </c>
       <c r="E7">
-        <v>20.59320443026093</v>
+        <v>17.47074651148238</v>
       </c>
       <c r="F7">
         <v>61.93604905825667</v>
       </c>
       <c r="G7">
-        <v>17.47074651148238</v>
+        <v>20.59320443026093</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.62349824992905</v>
+      </c>
+      <c r="C8">
         <v>36.86500804086652</v>
-      </c>
-      <c r="C8">
-        <v>29.62349824992905</v>
       </c>
       <c r="D8">
         <v>2.712599435463177</v>
       </c>
       <c r="E8">
-        <v>22.14267450779852</v>
+        <v>17.79311912270235</v>
       </c>
       <c r="F8">
         <v>60.06420636949914</v>
       </c>
       <c r="G8">
-        <v>17.79311912270235</v>
+        <v>22.14267450779852</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.56122813280971</v>
+      </c>
+      <c r="C9">
         <v>49.92859692966798</v>
-      </c>
-      <c r="C9">
-        <v>28.56122813280971</v>
       </c>
       <c r="D9">
         <v>2.002860207365034</v>
       </c>
       <c r="E9">
-        <v>27.97279727972797</v>
+        <v>16.001600160016</v>
       </c>
       <c r="F9">
         <v>56.02560256025603</v>
       </c>
       <c r="G9">
-        <v>16.001600160016</v>
+        <v>27.97279727972797</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.23721802081313</v>
+      </c>
+      <c r="C10">
         <v>35.46635640876479</v>
-      </c>
-      <c r="C10">
-        <v>30.23721802081313</v>
       </c>
       <c r="D10">
         <v>2.81957353745216</v>
       </c>
       <c r="E10">
-        <v>21.40349508503666</v>
+        <v>18.24777656420658</v>
       </c>
       <c r="F10">
         <v>60.34872835075674</v>
       </c>
       <c r="G10">
-        <v>18.24777656420658</v>
+        <v>21.40349508503666</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>29.1347322797188</v>
+      </c>
+      <c r="C11">
         <v>33.61171309265817</v>
-      </c>
-      <c r="C11">
-        <v>29.1347322797188</v>
       </c>
       <c r="D11">
         <v>2.975153325994653</v>
       </c>
       <c r="E11">
-        <v>20.65280935368626</v>
+        <v>17.90191620656057</v>
       </c>
       <c r="F11">
         <v>61.44527443975317</v>
       </c>
       <c r="G11">
-        <v>17.90191620656057</v>
+        <v>20.65280935368626</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.71223398679107</v>
+      </c>
+      <c r="C12">
         <v>31.76040465457595</v>
-      </c>
-      <c r="C12">
-        <v>29.71223398679107</v>
       </c>
       <c r="D12">
         <v>3.14857449354293</v>
       </c>
       <c r="E12">
-        <v>19.66921759736413</v>
+        <v>18.40078556762942</v>
       </c>
       <c r="F12">
         <v>61.92999683500646</v>
       </c>
       <c r="G12">
-        <v>18.40078556762942</v>
+        <v>19.66921759736413</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.31331150502427</v>
+      </c>
+      <c r="C13">
         <v>45.19589025629445</v>
-      </c>
-      <c r="C13">
-        <v>25.31331150502427</v>
       </c>
       <c r="D13">
         <v>2.212590557082188</v>
       </c>
       <c r="E13">
-        <v>26.5064229903324</v>
+        <v>14.84571579923189</v>
       </c>
       <c r="F13">
         <v>58.6478612104357</v>
       </c>
       <c r="G13">
-        <v>14.84571579923189</v>
+        <v>26.5064229903324</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.1805802249852</v>
+      </c>
+      <c r="C14">
         <v>34.24610223011644</v>
-      </c>
-      <c r="C14">
-        <v>30.1805802249852</v>
       </c>
       <c r="D14">
         <v>2.920040340008644</v>
       </c>
       <c r="E14">
-        <v>20.82758206805498</v>
+        <v>18.35503810838385</v>
       </c>
       <c r="F14">
         <v>60.81737982356119</v>
       </c>
       <c r="G14">
-        <v>18.35503810838385</v>
+        <v>20.82758206805498</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.40816825629738</v>
+      </c>
+      <c r="C15">
         <v>37.39300562484715</v>
-      </c>
-      <c r="C15">
-        <v>29.40816825629738</v>
       </c>
       <c r="D15">
         <v>2.674296926095487</v>
       </c>
       <c r="E15">
-        <v>22.41771131148742</v>
+        <v>17.63067223810571</v>
       </c>
       <c r="F15">
         <v>59.95161645040686</v>
       </c>
       <c r="G15">
-        <v>17.63067223810571</v>
+        <v>22.41771131148742</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>22.98095863427446</v>
+      </c>
+      <c r="C16">
         <v>47.66907419566645</v>
-      </c>
-      <c r="C16">
-        <v>22.98095863427446</v>
       </c>
       <c r="D16">
         <v>2.097796143250689</v>
       </c>
       <c r="E16">
-        <v>27.93382070026933</v>
+        <v>13.4667179684494</v>
       </c>
       <c r="F16">
         <v>58.59946133128126</v>
       </c>
       <c r="G16">
-        <v>13.4667179684494</v>
+        <v>27.93382070026933</v>
       </c>
     </row>
   </sheetData>
